--- a/exports/trend_1d/IDFCFIRSTB_full_report.xlsx
+++ b/exports/trend_1d/IDFCFIRSTB_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>12.2</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42348</v>
+        <v>42349</v>
       </c>
       <c r="H2" t="n">
-        <v>56.85</v>
+        <v>55.3</v>
       </c>
       <c r="I2" t="n">
         <v>56.0179</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>-10.89</v>
+        <v>-13.32</v>
       </c>
       <c r="L2" t="n">
         <v>13.95</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>14.87</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42397</v>
+        <v>42398</v>
       </c>
       <c r="H3" t="n">
-        <v>50.75</v>
+        <v>52.55</v>
       </c>
       <c r="I3" t="n">
         <v>51.7776791304143</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K3" t="n">
-        <v>8.23</v>
+        <v>4.97</v>
       </c>
       <c r="L3" t="n">
         <v>12.84</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>18.32</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42426</v>
+        <v>42429</v>
       </c>
       <c r="H4" t="n">
-        <v>47.1</v>
+        <v>45.55</v>
       </c>
       <c r="I4" t="n">
         <v>46.54820547772815</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.37</v>
+        <v>-13.32</v>
       </c>
       <c r="L4" t="n">
         <v>14.37</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>18.96</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42467</v>
+        <v>42468</v>
       </c>
       <c r="H5" t="n">
-        <v>50.35</v>
+        <v>52.15</v>
       </c>
       <c r="I5" t="n">
         <v>50.86654580825346</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K5" t="n">
-        <v>-10.54</v>
+        <v>-14.49</v>
       </c>
       <c r="L5" t="n">
-        <v>13.06</v>
+        <v>15.04</v>
       </c>
       <c r="M5" t="n">
         <v>2.48</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>12.94</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42487</v>
+        <v>42488</v>
       </c>
       <c r="H6" t="n">
-        <v>49.85</v>
+        <v>47.4</v>
       </c>
       <c r="I6" t="n">
         <v>49.50134726137634</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.41</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>5.08</v>
+        <v>10.26</v>
       </c>
       <c r="M6" t="n">
         <v>6.14</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>15.08</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42559</v>
+        <v>42562</v>
       </c>
       <c r="H7" t="n">
-        <v>47.5</v>
+        <v>48.05</v>
       </c>
       <c r="I7" t="n">
         <v>47.5252828846064</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.21</v>
+        <v>-1.37</v>
       </c>
       <c r="L7" t="n">
         <v>6.33</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>7.03</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42682</v>
+        <v>42683</v>
       </c>
       <c r="H8" t="n">
-        <v>72.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>72.24714346686264</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K8" t="n">
-        <v>50.47</v>
+        <v>49.64</v>
       </c>
       <c r="L8" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>2.04</v>
+        <v>8.58</v>
       </c>
       <c r="N8" t="n">
         <v>4.36</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.16</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42745</v>
+        <v>42746</v>
       </c>
       <c r="H9" t="n">
-        <v>61.85</v>
+        <v>62.95</v>
       </c>
       <c r="I9" t="n">
         <v>62.70437202706373</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K9" t="n">
-        <v>13.98</v>
+        <v>12.45</v>
       </c>
       <c r="L9" t="n">
         <v>4.87</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42765</v>
+        <v>42766</v>
       </c>
       <c r="H10" t="n">
-        <v>61.8</v>
+        <v>59.95</v>
       </c>
       <c r="I10" t="n">
         <v>60.72755864735131</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.83</v>
+        <v>-4.77</v>
       </c>
       <c r="L10" t="n">
-        <v>2.22</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
         <v>2.74</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42851</v>
+        <v>42852</v>
       </c>
       <c r="H11" t="n">
-        <v>61.2</v>
+        <v>65.2</v>
       </c>
       <c r="I11" t="n">
         <v>61.8765451228208</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.09</v>
+        <v>-8.76</v>
       </c>
       <c r="L11" t="n">
-        <v>6.92</v>
+        <v>9.67</v>
       </c>
       <c r="M11" t="n">
         <v>6.06</v>
       </c>
       <c r="N11" t="n">
-        <v>3.03</v>
+        <v>6.54</v>
       </c>
       <c r="O11" t="n">
         <v>-2.99</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>10.21</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42873</v>
+        <v>42874</v>
       </c>
       <c r="H12" t="n">
-        <v>61.6</v>
+        <v>60.65</v>
       </c>
       <c r="I12" t="n">
         <v>61.26190638338299</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.52</v>
+        <v>-6.98</v>
       </c>
       <c r="L12" t="n">
-        <v>6.13</v>
+        <v>7.67</v>
       </c>
       <c r="M12" t="n">
         <v>0.47</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>7.96</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42920</v>
+        <v>42921</v>
       </c>
       <c r="H13" t="n">
-        <v>56.65</v>
+        <v>62.35</v>
       </c>
       <c r="I13" t="n">
         <v>57.85972179628928</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K13" t="n">
-        <v>6.6</v>
+        <v>-2.8</v>
       </c>
       <c r="L13" t="n">
-        <v>2.14</v>
+        <v>6.68</v>
       </c>
       <c r="M13" t="n">
         <v>1.75</v>
       </c>
       <c r="N13" t="n">
-        <v>3.09</v>
+        <v>10.06</v>
       </c>
       <c r="O13" t="n">
         <v>-1.54</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>11.31</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42936</v>
+        <v>42937</v>
       </c>
       <c r="H14" t="n">
-        <v>61.35</v>
+        <v>60.35</v>
       </c>
       <c r="I14" t="n">
         <v>60.54565762650914</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.6</v>
+        <v>-3.21</v>
       </c>
       <c r="L14" t="n">
         <v>8.9</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>11.29</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42990</v>
+        <v>42991</v>
       </c>
       <c r="H15" t="n">
-        <v>57.4</v>
+        <v>58.9</v>
       </c>
       <c r="I15" t="n">
         <v>58.34481478997011</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K15" t="n">
-        <v>4.89</v>
+        <v>2.4</v>
       </c>
       <c r="L15" t="n">
         <v>2.32</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.75</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H16" t="n">
-        <v>57.15</v>
+        <v>56.35</v>
       </c>
       <c r="I16" t="n">
         <v>56.54614837435406</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.97</v>
+        <v>-4.33</v>
       </c>
       <c r="L16" t="n">
         <v>5.52</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>9.26</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43039</v>
+        <v>43040</v>
       </c>
       <c r="H17" t="n">
-        <v>56.65</v>
+        <v>62.3</v>
       </c>
       <c r="I17" t="n">
         <v>60.20976631839837</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.53</v>
+        <v>-10.56</v>
       </c>
       <c r="L17" t="n">
-        <v>7.36</v>
+        <v>13.22</v>
       </c>
       <c r="M17" t="n">
         <v>2.54</v>
       </c>
       <c r="N17" t="n">
-        <v>3.83</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="O17" t="n">
         <v>-1.4</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>13.33</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43073</v>
+        <v>43074</v>
       </c>
       <c r="H18" t="n">
-        <v>54.35</v>
+        <v>53.8</v>
       </c>
       <c r="I18" t="n">
         <v>53.99632207272653</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K18" t="n">
-        <v>-12.76</v>
+        <v>-13.64</v>
       </c>
       <c r="L18" t="n">
-        <v>13.32</v>
+        <v>13.96</v>
       </c>
       <c r="M18" t="n">
         <v>0.62</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>6.43</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43104</v>
+        <v>43105</v>
       </c>
       <c r="H19" t="n">
-        <v>54.55</v>
+        <v>58.25</v>
       </c>
       <c r="I19" t="n">
         <v>55.25216568297068</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.39</v>
+        <v>-8.27</v>
       </c>
       <c r="L19" t="n">
-        <v>4.09</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="M19" t="n">
         <v>1.15</v>
       </c>
       <c r="N19" t="n">
-        <v>2.79</v>
+        <v>6.78</v>
       </c>
       <c r="O19" t="n">
         <v>-1.01</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43117</v>
+        <v>43118</v>
       </c>
       <c r="H20" t="n">
-        <v>60.75</v>
+        <v>58.3</v>
       </c>
       <c r="I20" t="n">
         <v>59.50695078967458</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K20" t="n">
-        <v>4.29</v>
+        <v>0.09</v>
       </c>
       <c r="L20" t="n">
         <v>6.18</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>18.95</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43262</v>
+        <v>43263</v>
       </c>
       <c r="H21" t="n">
-        <v>42.15</v>
+        <v>42.95</v>
       </c>
       <c r="I21" t="n">
         <v>42.92949106603515</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K21" t="n">
-        <v>27.7</v>
+        <v>26.33</v>
       </c>
       <c r="L21" t="n">
         <v>6.17</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>6</v>
+      </c>
+      <c r="U21" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>11.63</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43278</v>
+        <v>43279</v>
       </c>
       <c r="H22" t="n">
-        <v>40.95</v>
+        <v>39.3</v>
       </c>
       <c r="I22" t="n">
         <v>39.41538675453769</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.66</v>
+        <v>-8.5</v>
       </c>
       <c r="L22" t="n">
-        <v>6.17</v>
+        <v>9.66</v>
       </c>
       <c r="M22" t="n">
         <v>1.18</v>
       </c>
       <c r="N22" t="n">
-        <v>2.95</v>
+        <v>4.03</v>
       </c>
       <c r="O22" t="n">
         <v>1.9</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>12.62</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43308</v>
+        <v>43311</v>
       </c>
       <c r="H23" t="n">
-        <v>39.3</v>
+        <v>41.3</v>
       </c>
       <c r="I23" t="n">
         <v>40.88271340982049</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>-5.09</v>
       </c>
       <c r="L23" t="n">
-        <v>4.71</v>
+        <v>6.74</v>
       </c>
       <c r="M23" t="n">
         <v>1.93</v>
       </c>
       <c r="N23" t="n">
-        <v>3.74</v>
+        <v>5.09</v>
       </c>
       <c r="O23" t="n">
         <v>-4.03</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>12.24</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43353</v>
+        <v>43354</v>
       </c>
       <c r="H24" t="n">
-        <v>44.8</v>
+        <v>43.9</v>
       </c>
       <c r="I24" t="n">
         <v>44.46142235945061</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K24" t="n">
-        <v>8.470000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="L24" t="n">
         <v>6.05</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>12.04</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43425</v>
+        <v>43426</v>
       </c>
       <c r="H25" t="n">
-        <v>36.4</v>
+        <v>39</v>
       </c>
       <c r="I25" t="n">
         <v>38.34706350003469</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K25" t="n">
-        <v>17.08</v>
+        <v>11.16</v>
       </c>
       <c r="L25" t="n">
         <v>2.85</v>
@@ -1866,7 +2165,7 @@
         <v>1.71</v>
       </c>
       <c r="N25" t="n">
-        <v>6.85</v>
+        <v>7.14</v>
       </c>
       <c r="O25" t="n">
         <v>-2.01</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.38</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43497</v>
+        <v>43500</v>
       </c>
       <c r="H26" t="n">
-        <v>44.8</v>
+        <v>43.3</v>
       </c>
       <c r="I26" t="n">
         <v>43.76471706069347</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K26" t="n">
-        <v>14.87</v>
+        <v>11.03</v>
       </c>
       <c r="L26" t="n">
         <v>9.359999999999999</v>
@@ -1923,7 +2234,7 @@
         <v>1.51</v>
       </c>
       <c r="N26" t="n">
-        <v>3.21</v>
+        <v>3.35</v>
       </c>
       <c r="O26" t="n">
         <v>7.14</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>11.96</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43524</v>
+        <v>43525</v>
       </c>
       <c r="H27" t="n">
-        <v>44.75</v>
+        <v>47.5</v>
       </c>
       <c r="I27" t="n">
         <v>46.50789361046017</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.35</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>6.81</v>
+        <v>10.16</v>
       </c>
       <c r="M27" t="n">
         <v>1.8</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>11.95</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43581</v>
+        <v>43585</v>
       </c>
       <c r="H28" t="n">
-        <v>51.95</v>
+        <v>49.95</v>
       </c>
       <c r="I28" t="n">
         <v>51.59655528406569</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K28" t="n">
-        <v>9.369999999999999</v>
+        <v>5.16</v>
       </c>
       <c r="L28" t="n">
         <v>4.95</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>9.67</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43684</v>
+        <v>43685</v>
       </c>
       <c r="H29" t="n">
-        <v>41.35</v>
+        <v>42.45</v>
       </c>
       <c r="I29" t="n">
         <v>42.4284510614571</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K29" t="n">
-        <v>17.22</v>
+        <v>15.02</v>
       </c>
       <c r="L29" t="n">
         <v>3.9</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>14.55</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43735</v>
+        <v>43738</v>
       </c>
       <c r="H30" t="n">
-        <v>42.5</v>
+        <v>40.2</v>
       </c>
       <c r="I30" t="n">
         <v>40.23954354095768</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K30" t="n">
-        <v>0.12</v>
+        <v>-5.3</v>
       </c>
       <c r="L30" t="n">
-        <v>5.06</v>
+        <v>7.18</v>
       </c>
       <c r="M30" t="n">
         <v>1.15</v>
       </c>
       <c r="N30" t="n">
-        <v>3.23</v>
+        <v>5.41</v>
       </c>
       <c r="O30" t="n">
         <v>2.66</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>14.33</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43768</v>
+        <v>43769</v>
       </c>
       <c r="H31" t="n">
-        <v>42.5</v>
+        <v>44.65</v>
       </c>
       <c r="I31" t="n">
         <v>42.81140588377168</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.72</v>
+        <v>-11.07</v>
       </c>
       <c r="L31" t="n">
-        <v>7.96</v>
+        <v>11.94</v>
       </c>
       <c r="M31" t="n">
         <v>4.89</v>
       </c>
       <c r="N31" t="n">
-        <v>4.63</v>
+        <v>5.06</v>
       </c>
       <c r="O31" t="n">
         <v>-5.41</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>13.19</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43808</v>
+        <v>43809</v>
       </c>
       <c r="H32" t="n">
-        <v>42.7</v>
+        <v>42.1</v>
       </c>
       <c r="I32" t="n">
         <v>42.53897296025249</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.37</v>
+        <v>-5.71</v>
       </c>
       <c r="L32" t="n">
         <v>8.4</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>11.37</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43831</v>
+        <v>43832</v>
       </c>
       <c r="H33" t="n">
-        <v>45.8</v>
+        <v>46.15</v>
       </c>
       <c r="I33" t="n">
         <v>46.14905723338821</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K33" t="n">
-        <v>-8.789999999999999</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>9.140000000000001</v>
+        <v>10.57</v>
       </c>
       <c r="M33" t="n">
         <v>0.59</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>7.48</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43859</v>
+        <v>43860</v>
       </c>
       <c r="H34" t="n">
-        <v>44.05</v>
+        <v>40.75</v>
       </c>
       <c r="I34" t="n">
         <v>42.69667860957658</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.55</v>
+        <v>-11.7</v>
       </c>
       <c r="L34" t="n">
-        <v>10.4</v>
+        <v>12.78</v>
       </c>
       <c r="M34" t="n">
-        <v>3.33</v>
+        <v>3.41</v>
       </c>
       <c r="N34" t="n">
-        <v>3.96</v>
+        <v>7.49</v>
       </c>
       <c r="O34" t="n">
         <v>0.76</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>13.02</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H35" t="n">
-        <v>22.1</v>
+        <v>23.65</v>
       </c>
       <c r="I35" t="n">
         <v>22.10395957344113</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K35" t="n">
-        <v>45.77</v>
+        <v>41.96</v>
       </c>
       <c r="L35" t="n">
         <v>5.64</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>5</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>19.12</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44095</v>
+        <v>44096</v>
       </c>
       <c r="H36" t="n">
-        <v>29.45</v>
+        <v>28.7</v>
       </c>
       <c r="I36" t="n">
         <v>29.05644454369203</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K36" t="n">
-        <v>24.52</v>
+        <v>21.35</v>
       </c>
       <c r="L36" t="n">
         <v>5.29</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>15.82</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44112</v>
+        <v>44113</v>
       </c>
       <c r="H37" t="n">
-        <v>31.5</v>
+        <v>31.95</v>
       </c>
       <c r="I37" t="n">
         <v>31.80862792039743</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.76</v>
+        <v>-11.32</v>
       </c>
       <c r="L37" t="n">
-        <v>11.32</v>
+        <v>12.02</v>
       </c>
       <c r="M37" t="n">
         <v>1.3</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>12.7</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44272</v>
+        <v>44273</v>
       </c>
       <c r="H38" t="n">
-        <v>60.9</v>
+        <v>59.4</v>
       </c>
       <c r="I38" t="n">
         <v>59.42536353786079</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K38" t="n">
-        <v>90.61</v>
+        <v>85.92</v>
       </c>
       <c r="L38" t="n">
         <v>6.89</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>16.36</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44337</v>
+        <v>44340</v>
       </c>
       <c r="H39" t="n">
-        <v>57.25</v>
+        <v>59.25</v>
       </c>
       <c r="I39" t="n">
         <v>59.19329859959913</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K39" t="n">
-        <v>3.62</v>
+        <v>0.25</v>
       </c>
       <c r="L39" t="n">
         <v>4.97</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>11.08</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44376</v>
+        <v>44377</v>
       </c>
       <c r="H40" t="n">
-        <v>55.85</v>
+        <v>54.2</v>
       </c>
       <c r="I40" t="n">
         <v>55.448567074029</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K40" t="n">
-        <v>-5.74</v>
+        <v>-8.52</v>
       </c>
       <c r="L40" t="n">
-        <v>7</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="M40" t="n">
         <v>1.91</v>
       </c>
       <c r="N40" t="n">
-        <v>2.23</v>
+        <v>2.95</v>
       </c>
       <c r="O40" t="n">
         <v>3.49</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.8</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44452</v>
+        <v>44453</v>
       </c>
       <c r="H41" t="n">
-        <v>46.85</v>
+        <v>47.95</v>
       </c>
       <c r="I41" t="n">
         <v>47.30475874335212</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K41" t="n">
-        <v>13.56</v>
+        <v>11.53</v>
       </c>
       <c r="L41" t="n">
         <v>3.78</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>10.38</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H42" t="n">
-        <v>48.55</v>
+        <v>46.35</v>
       </c>
       <c r="I42" t="n">
         <v>46.84976462538372</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K42" t="n">
-        <v>1.25</v>
+        <v>-3.34</v>
       </c>
       <c r="L42" t="n">
         <v>5.42</v>
       </c>
       <c r="M42" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="N42" t="n">
         <v>5.35</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>13.17</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44539</v>
+        <v>44540</v>
       </c>
       <c r="H43" t="n">
-        <v>49.5</v>
+        <v>52.1</v>
       </c>
       <c r="I43" t="n">
         <v>50.90320413553091</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.8</v>
+        <v>-12.41</v>
       </c>
       <c r="L43" t="n">
-        <v>7.12</v>
+        <v>13.27</v>
       </c>
       <c r="M43" t="n">
         <v>1.05</v>
       </c>
       <c r="N43" t="n">
-        <v>3.81</v>
+        <v>5.25</v>
       </c>
       <c r="O43" t="n">
         <v>-4.53</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>12.91</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44547</v>
+        <v>44550</v>
       </c>
       <c r="H44" t="n">
-        <v>48.05</v>
+        <v>45.6</v>
       </c>
       <c r="I44" t="n">
         <v>46.4612014970708</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K44" t="n">
-        <v>-7.77</v>
+        <v>-12.48</v>
       </c>
       <c r="L44" t="n">
-        <v>8.06</v>
+        <v>13.82</v>
       </c>
       <c r="M44" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="N44" t="n">
-        <v>3.32</v>
+        <v>5.1</v>
       </c>
       <c r="O44" t="n">
         <v>5.25</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>13.89</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H45" t="n">
-        <v>41.7</v>
+        <v>43.65</v>
       </c>
       <c r="I45" t="n">
         <v>42.61475431722019</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K45" t="n">
-        <v>8.550000000000001</v>
+        <v>4.28</v>
       </c>
       <c r="L45" t="n">
         <v>10.96</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>12.99</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44680</v>
+        <v>44683</v>
       </c>
       <c r="H46" t="n">
-        <v>39.5</v>
+        <v>38.85</v>
       </c>
       <c r="I46" t="n">
         <v>38.91406772322465</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K46" t="n">
-        <v>-9.51</v>
+        <v>-11</v>
       </c>
       <c r="L46" t="n">
-        <v>10.31</v>
+        <v>12.26</v>
       </c>
       <c r="M46" t="n">
         <v>0.62</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>11.32</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44743</v>
+        <v>44746</v>
       </c>
       <c r="H47" t="n">
-        <v>32.25</v>
+        <v>34.05</v>
       </c>
       <c r="I47" t="n">
         <v>33.26778396166881</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K47" t="n">
-        <v>16.99</v>
+        <v>12.36</v>
       </c>
       <c r="L47" t="n">
         <v>5.02</v>
@@ -3120,7 +3683,7 @@
         <v>2.29</v>
       </c>
       <c r="N47" t="n">
-        <v>4.2</v>
+        <v>5.58</v>
       </c>
       <c r="O47" t="n">
         <v>-1.65</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>13.29</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H48" t="n">
-        <v>48.7</v>
+        <v>47.25</v>
       </c>
       <c r="I48" t="n">
         <v>47.34904761681783</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K48" t="n">
-        <v>43.02</v>
+        <v>38.77</v>
       </c>
       <c r="L48" t="n">
         <v>4.26</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>11.98</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44837</v>
+        <v>44838</v>
       </c>
       <c r="H49" t="n">
-        <v>49.35</v>
+        <v>53.2</v>
       </c>
       <c r="I49" t="n">
         <v>52.15474264330815</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.44</v>
+        <v>-12.59</v>
       </c>
       <c r="L49" t="n">
-        <v>8.470000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="M49" t="n">
-        <v>1.71</v>
+        <v>3.75</v>
       </c>
       <c r="N49" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="O49" t="n">
         <v>-2.98</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>13.45</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H50" t="n">
-        <v>58.95</v>
+        <v>56.95</v>
       </c>
       <c r="I50" t="n">
         <v>58.38913219720592</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K50" t="n">
-        <v>10.81</v>
+        <v>7.05</v>
       </c>
       <c r="L50" t="n">
         <v>4.23</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>12.28</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44928</v>
+        <v>44929</v>
       </c>
       <c r="H51" t="n">
-        <v>61.15</v>
+        <v>61.35</v>
       </c>
       <c r="I51" t="n">
         <v>61.26768262098469</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K51" t="n">
-        <v>-7.37</v>
+        <v>-7.73</v>
       </c>
       <c r="L51" t="n">
-        <v>7.99</v>
+        <v>8.25</v>
       </c>
       <c r="M51" t="n">
         <v>1.41</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>12.05</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44974</v>
+        <v>44977</v>
       </c>
       <c r="H52" t="n">
-        <v>55.9</v>
+        <v>55</v>
       </c>
       <c r="I52" t="n">
         <v>55.44873805463562</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K52" t="n">
-        <v>-8.880000000000001</v>
+        <v>-10.35</v>
       </c>
       <c r="L52" t="n">
         <v>11.65</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>9.17</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45037</v>
+        <v>45040</v>
       </c>
       <c r="H53" t="n">
-        <v>56.45</v>
+        <v>58.25</v>
       </c>
       <c r="I53" t="n">
         <v>57.02618409181908</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.64</v>
+        <v>-5.91</v>
       </c>
       <c r="L53" t="n">
-        <v>5.64</v>
+        <v>6.09</v>
       </c>
       <c r="M53" t="n">
         <v>1.55</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45205</v>
+        <v>45208</v>
       </c>
       <c r="H54" t="n">
-        <v>91.40000000000001</v>
+        <v>90.05</v>
       </c>
       <c r="I54" t="n">
         <v>90.58292458173077</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K54" t="n">
-        <v>56.91</v>
+        <v>54.59</v>
       </c>
       <c r="L54" t="n">
         <v>3.09</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>7</v>
+      </c>
+      <c r="U54" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.54</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="H55" t="n">
-        <v>86.95</v>
+        <v>89.25</v>
       </c>
       <c r="I55" t="n">
         <v>88.7751299867459</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K55" t="n">
-        <v>3.44</v>
+        <v>0.89</v>
       </c>
       <c r="L55" t="n">
         <v>3.66</v>
@@ -3576,7 +4235,7 @@
         <v>2.6</v>
       </c>
       <c r="N55" t="n">
-        <v>1.78</v>
+        <v>2.65</v>
       </c>
       <c r="O55" t="n">
         <v>-1.48</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>6.91</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45299</v>
+        <v>45300</v>
       </c>
       <c r="H56" t="n">
-        <v>85.45</v>
+        <v>84.25</v>
       </c>
       <c r="I56" t="n">
         <v>85.40459594533777</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.26</v>
+        <v>-5.6</v>
       </c>
       <c r="L56" t="n">
-        <v>5.27</v>
+        <v>5.88</v>
       </c>
       <c r="M56" t="n">
         <v>3.32</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="H57" t="n">
-        <v>80.65000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I57" t="n">
         <v>81.26105458641658</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K57" t="n">
-        <v>4.27</v>
+        <v>2.08</v>
       </c>
       <c r="L57" t="n">
         <v>6.41</v>
       </c>
       <c r="M57" t="n">
-        <v>1.25</v>
+        <v>2.05</v>
       </c>
       <c r="N57" t="n">
         <v>4.31</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>7.11</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45418</v>
+        <v>45419</v>
       </c>
       <c r="H58" t="n">
-        <v>80.05</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="I58" t="n">
         <v>79.54737669186386</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K58" t="n">
-        <v>-2.97</v>
+        <v>-5.64</v>
       </c>
       <c r="L58" t="n">
-        <v>3.15</v>
+        <v>6.18</v>
       </c>
       <c r="M58" t="n">
         <v>1.65</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45461</v>
+        <v>45462</v>
       </c>
       <c r="H59" t="n">
-        <v>81.45999999999999</v>
+        <v>82.17</v>
       </c>
       <c r="I59" t="n">
         <v>81.68124828708038</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.64</v>
+        <v>-5.55</v>
       </c>
       <c r="L59" t="n">
-        <v>4.86</v>
+        <v>7.26</v>
       </c>
       <c r="M59" t="n">
         <v>5.56</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>8.4</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45491</v>
+        <v>45492</v>
       </c>
       <c r="H60" t="n">
-        <v>77.73999999999999</v>
+        <v>76.02</v>
       </c>
       <c r="I60" t="n">
         <v>77.36509902937541</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K60" t="n">
-        <v>-5.39</v>
+        <v>-7.48</v>
       </c>
       <c r="L60" t="n">
-        <v>5.55</v>
+        <v>7.69</v>
       </c>
       <c r="M60" t="n">
         <v>0.21</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.25</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45749</v>
+        <v>45750</v>
       </c>
       <c r="H61" t="n">
-        <v>57.19</v>
+        <v>60.35</v>
       </c>
       <c r="I61" t="n">
         <v>58.10105547498423</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K61" t="n">
-        <v>24.77</v>
+        <v>20.61</v>
       </c>
       <c r="L61" t="n">
         <v>2.66</v>
@@ -3918,7 +4649,7 @@
         <v>2.76</v>
       </c>
       <c r="N61" t="n">
-        <v>4.4</v>
+        <v>5.53</v>
       </c>
       <c r="O61" t="n">
         <v>-2.21</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>177</v>
+        <v>178</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>10</v>
+      </c>
+      <c r="U61" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>12.12</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45852</v>
+        <v>45853</v>
       </c>
       <c r="H62" t="n">
-        <v>74.27</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="I62" t="n">
         <v>73.41096434629597</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K62" t="n">
-        <v>23.07</v>
+        <v>20.85</v>
       </c>
       <c r="L62" t="n">
         <v>13.07</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>8.25</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45904</v>
+        <v>45905</v>
       </c>
       <c r="H63" t="n">
-        <v>72.23</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I63" t="n">
         <v>72.55369275471639</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K63" t="n">
-        <v>0.96</v>
+        <v>0.45</v>
       </c>
       <c r="L63" t="n">
         <v>2.51</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>5.84</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H64" t="n">
-        <v>69.93000000000001</v>
+        <v>68.59</v>
       </c>
       <c r="I64" t="n">
         <v>69.04796842686669</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K64" t="n">
-        <v>-3.68</v>
+        <v>-5.52</v>
       </c>
       <c r="L64" t="n">
-        <v>4.06</v>
+        <v>5.76</v>
       </c>
       <c r="M64" t="n">
         <v>0.49</v>
       </c>
       <c r="N64" t="n">
-        <v>1.16</v>
+        <v>1.92</v>
       </c>
       <c r="O64" t="n">
         <v>0.51</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>5.81</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="H65" t="n">
-        <v>71.98999999999999</v>
+        <v>73.45</v>
       </c>
       <c r="I65" t="n">
         <v>72.57314572285037</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.96</v>
+        <v>-7.09</v>
       </c>
       <c r="L65" t="n">
-        <v>5.92</v>
+        <v>7.49</v>
       </c>
       <c r="M65" t="n">
         <v>0.5600000000000001</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>6.44</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="H66" t="n">
-        <v>82.09</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="I66" t="n">
         <v>81.72662919306519</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K66" t="n">
-        <v>11.76</v>
+        <v>10.97</v>
       </c>
       <c r="L66" t="n">
         <v>2.37</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>6.41</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H67" t="n">
-        <v>64.86</v>
+        <v>66.91</v>
       </c>
       <c r="I67" t="n">
         <v>66.42515286882183</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K67" t="n">
-        <v>20.43</v>
+        <v>17.91</v>
       </c>
       <c r="L67" t="n">
         <v>5.74</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>11.02</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="H68" t="n">
-        <v>83.8</v>
+        <v>80.55</v>
       </c>
       <c r="I68" t="n">
         <v>82.48454173024297</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="K68" t="n">
-        <v>25.24</v>
+        <v>20.39</v>
       </c>
       <c r="L68" t="n">
         <v>1.33</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>6</v>
+      </c>
+      <c r="U68" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,14 @@
       <c r="Q69" t="n">
         <v>21</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8995,7 +9830,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.6</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="6">
@@ -9005,7 +9840,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -9015,7 +9850,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8">
@@ -9025,7 +9860,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -9035,7 +9870,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76.5</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="10">
@@ -9045,7 +9880,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115.2</v>
+        <v>116.2</v>
       </c>
     </row>
     <row r="11">
@@ -9055,7 +9890,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -9065,7 +9900,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
@@ -9075,7 +9910,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>37.3</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="14">
@@ -9085,7 +9920,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.38</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="15">
@@ -9095,7 +9930,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.72</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="16">
@@ -9105,7 +9940,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.99</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="17">
@@ -9115,7 +9950,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>90.61</v>
+        <v>85.92</v>
       </c>
     </row>
     <row r="18">
@@ -9125,7 +9960,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.8</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="19">
@@ -9135,7 +9970,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.45</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="20">
@@ -9145,7 +9980,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.74</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="21">
@@ -9155,7 +9990,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.37</v>
+        <v>15.04</v>
       </c>
     </row>
     <row r="22">
@@ -9165,7 +10000,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
@@ -9175,7 +10010,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -9185,7 +10020,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="25">
@@ -9205,7 +10040,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.59</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="27">
@@ -9215,7 +10050,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.32</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="28">
@@ -9225,7 +10060,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29">
